--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2021_metropolitana_provincial.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:16</t>
+    <t xml:space="preserve">2026-10-05 05:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
